--- a/Employee_Reports_wi52/Noey Francisco Canonizado Q0621.xlsx
+++ b/Employee_Reports_wi52/Noey Francisco Canonizado Q0621.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -790,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1453,11 +1453,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1600,11 +1600,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1698,11 +1698,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1747,11 +1747,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1784,11 +1784,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1858,11 +1858,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1907,11 +1907,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1920,6 +1920,43 @@
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2338,7 +2375,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2367,7 +2404,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2396,7 +2433,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2425,7 +2462,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2454,7 +2491,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2483,7 +2520,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2578,7 +2615,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2607,7 +2644,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2673,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2665,7 +2702,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2694,7 +2731,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2723,7 +2760,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2752,7 +2789,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2781,7 +2818,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2847,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2839,7 +2876,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2868,7 +2905,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2897,7 +2934,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2963,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2955,7 +2992,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2984,7 +3021,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3050,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3042,7 +3079,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3108,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3100,7 +3137,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3129,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3158,7 +3195,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
